--- a/starrings.xlsx
+++ b/starrings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C874A105-A763-41D9-A61C-C568BB139B00}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B091862-3614-401B-B5F8-C4F991E0159F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Ava Canning</t>
   </si>
@@ -124,6 +124,51 @@
   </si>
   <si>
     <t>Leah Mullett</t>
+  </si>
+  <si>
+    <t>Daphne Deacon</t>
+  </si>
+  <si>
+    <t>Margaret O'Donoghue</t>
+  </si>
+  <si>
+    <t>Alison Crawford</t>
+  </si>
+  <si>
+    <t>Sadhbh Smyth</t>
+  </si>
+  <si>
+    <t>Vida Reynolds</t>
+  </si>
+  <si>
+    <t>Sriya Komati Reddy</t>
+  </si>
+  <si>
+    <t>Cathy Treneman</t>
+  </si>
+  <si>
+    <t>Rachel Sparrow</t>
+  </si>
+  <si>
+    <t>Lorraine Bagnall</t>
+  </si>
+  <si>
+    <t>Lavanya Rajesh</t>
+  </si>
+  <si>
+    <t>Helen O'Kelly</t>
+  </si>
+  <si>
+    <t>Ruth McGonnell</t>
+  </si>
+  <si>
+    <t>Emily Bowe</t>
+  </si>
+  <si>
+    <t>Aisling Dunne</t>
+  </si>
+  <si>
+    <t>Caoimhe O'Brien</t>
   </si>
 </sst>
 </file>
@@ -176,10 +221,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -445,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -457,7 +498,7 @@
     <col min="7" max="7" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1.1000000000000001</v>
       </c>
@@ -476,8 +517,11 @@
       <c r="F1">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -496,8 +540,11 @@
       <c r="F2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -516,8 +563,11 @@
       <c r="F3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -536,8 +586,11 @@
       <c r="F4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -556,8 +609,11 @@
       <c r="F5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -576,8 +632,11 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -586,6 +645,54 @@
       </c>
       <c r="E7" t="s">
         <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
